--- a/09-supplementary/supplementary-materials-index.xlsx
+++ b/09-supplementary/supplementary-materials-index.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\6th Semester\KBS\KBS CEP\OUR SLR\09-supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -96,13 +96,13 @@
     <t>S6</t>
   </si>
   <si>
-    <t>Included studies BibTeX</t>
-  </si>
-  <si>
     <t>included-studies.bib</t>
   </si>
   <si>
-    <t>BibTeX metadata for citation management and replication</t>
+    <t xml:space="preserve">Included studies </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> metadata for citation management and replication</t>
   </si>
 </sst>
 </file>
@@ -1021,10 +1021,10 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
         <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
